--- a/backend/Vehicle_door_numbers.xlsx
+++ b/backend/Vehicle_door_numbers.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lokesh/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lokesh/IdeaProjects/NTPC_EM/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A1DE05E-AA99-C048-94CD-5F114787C886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B5E38E-65F5-124D-B69A-5FAF4D1C8E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="378">
   <si>
     <t>SL.NO</t>
   </si>
@@ -228,9 +228,6 @@
     <t>BB-114</t>
   </si>
   <si>
-    <t>COAL TIPPERS</t>
-  </si>
-  <si>
     <t>CT-01</t>
   </si>
   <si>
@@ -594,9 +591,6 @@
     <t>SC-133</t>
   </si>
   <si>
-    <t>WATER TANKERS</t>
-  </si>
-  <si>
     <t>BHARAT BENZ 3128</t>
   </si>
   <si>
@@ -696,9 +690,6 @@
     <t>WT-30</t>
   </si>
   <si>
-    <t>DIESEL TANKERS</t>
-  </si>
-  <si>
     <t>Eicher Pro 5016</t>
   </si>
   <si>
@@ -738,9 +729,6 @@
     <t>DT-11</t>
   </si>
   <si>
-    <t>DIESEL BOWSER</t>
-  </si>
-  <si>
     <t>Eicher Pro 3019 M</t>
   </si>
   <si>
@@ -768,9 +756,6 @@
     <t>SV-03</t>
   </si>
   <si>
-    <t>HYDRA CRANES</t>
-  </si>
-  <si>
     <t>ESCORT HYDRA14</t>
   </si>
   <si>
@@ -822,9 +807,6 @@
     <t>BU-06</t>
   </si>
   <si>
-    <t>VAN</t>
-  </si>
-  <si>
     <t>EICHER PRO1110H</t>
   </si>
   <si>
@@ -1165,6 +1147,18 @@
   </si>
   <si>
     <t>VO-166</t>
+  </si>
+  <si>
+    <t>WATER TANKER</t>
+  </si>
+  <si>
+    <t>DIESEL TANKER</t>
+  </si>
+  <si>
+    <t>Service Van</t>
+  </si>
+  <si>
+    <t>Crane</t>
   </si>
 </sst>
 </file>
@@ -2436,13 +2430,13 @@
         <v>60</v>
       </c>
       <c r="B62" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>67</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.2">
@@ -2450,13 +2444,13 @@
         <v>61</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.2">
@@ -2464,13 +2458,13 @@
         <v>62</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.2">
@@ -2478,13 +2472,13 @@
         <v>63</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.2">
@@ -2492,13 +2486,13 @@
         <v>64</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.2">
@@ -2506,13 +2500,13 @@
         <v>65</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.2">
@@ -2520,13 +2514,13 @@
         <v>66</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.2">
@@ -2534,13 +2528,13 @@
         <v>67</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.2">
@@ -2548,13 +2542,13 @@
         <v>68</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.2">
@@ -2562,13 +2556,13 @@
         <v>69</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.2">
@@ -2576,13 +2570,13 @@
         <v>70</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.2">
@@ -2590,13 +2584,13 @@
         <v>71</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.2">
@@ -2604,13 +2598,13 @@
         <v>72</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.2">
@@ -2618,13 +2612,13 @@
         <v>73</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.2">
@@ -2632,13 +2626,13 @@
         <v>74</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C76" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.2">
@@ -2646,13 +2640,13 @@
         <v>75</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C77" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.2">
@@ -2660,13 +2654,13 @@
         <v>76</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C78" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.2">
@@ -2674,13 +2668,13 @@
         <v>77</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.2">
@@ -2688,13 +2682,13 @@
         <v>78</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.2">
@@ -2702,13 +2696,13 @@
         <v>79</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.2">
@@ -2716,13 +2710,13 @@
         <v>80</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.2">
@@ -2730,13 +2724,13 @@
         <v>81</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.2">
@@ -2744,13 +2738,13 @@
         <v>82</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.2">
@@ -2758,13 +2752,13 @@
         <v>83</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.2">
@@ -2772,13 +2766,13 @@
         <v>84</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C86" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.2">
@@ -2786,13 +2780,13 @@
         <v>85</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C87" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.2">
@@ -2800,13 +2794,13 @@
         <v>86</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C88" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.2">
@@ -2814,13 +2808,13 @@
         <v>87</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C89" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.2">
@@ -2828,13 +2822,13 @@
         <v>88</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C90" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.2">
@@ -2842,13 +2836,13 @@
         <v>89</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C91" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.2">
@@ -2856,13 +2850,13 @@
         <v>90</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C92" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.2">
@@ -2870,13 +2864,13 @@
         <v>91</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C93" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.2">
@@ -2884,13 +2878,13 @@
         <v>92</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C94" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.2">
@@ -2898,13 +2892,13 @@
         <v>93</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C95" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.2">
@@ -2912,13 +2906,13 @@
         <v>94</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C96" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
@@ -2926,13 +2920,13 @@
         <v>95</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C97" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
@@ -2940,13 +2934,13 @@
         <v>96</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C98" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
@@ -2954,13 +2948,13 @@
         <v>97</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C99" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
@@ -2968,13 +2962,13 @@
         <v>98</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C100" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
@@ -2982,13 +2976,13 @@
         <v>99</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C101" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
@@ -2996,13 +2990,13 @@
         <v>100</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C102" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
@@ -3010,13 +3004,13 @@
         <v>101</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C103" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
@@ -3024,13 +3018,13 @@
         <v>102</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C104" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
@@ -3038,13 +3032,13 @@
         <v>103</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C105" s="3" t="s">
         <v>5</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
@@ -3052,13 +3046,13 @@
         <v>104</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C106" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D106" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
@@ -3066,13 +3060,13 @@
         <v>105</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
@@ -3083,10 +3077,10 @@
         <v>4</v>
       </c>
       <c r="C108" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D108" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
@@ -3097,10 +3091,10 @@
         <v>4</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
@@ -3111,10 +3105,10 @@
         <v>4</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
@@ -3125,10 +3119,10 @@
         <v>4</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
@@ -3139,10 +3133,10 @@
         <v>4</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
@@ -3153,10 +3147,10 @@
         <v>4</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
@@ -3167,10 +3161,10 @@
         <v>4</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
@@ -3181,10 +3175,10 @@
         <v>4</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
@@ -3195,10 +3189,10 @@
         <v>4</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
@@ -3209,10 +3203,10 @@
         <v>4</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
@@ -3223,10 +3217,10 @@
         <v>4</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
@@ -3237,10 +3231,10 @@
         <v>4</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
@@ -3251,10 +3245,10 @@
         <v>4</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
@@ -3265,10 +3259,10 @@
         <v>4</v>
       </c>
       <c r="C121" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D121" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="D121" s="4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
@@ -3279,10 +3273,10 @@
         <v>4</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
@@ -3293,10 +3287,10 @@
         <v>4</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
@@ -3307,10 +3301,10 @@
         <v>4</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
@@ -3321,10 +3315,10 @@
         <v>4</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
@@ -3335,10 +3329,10 @@
         <v>4</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
@@ -3349,10 +3343,10 @@
         <v>4</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
@@ -3363,10 +3357,10 @@
         <v>4</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
@@ -3377,10 +3371,10 @@
         <v>4</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
@@ -3391,10 +3385,10 @@
         <v>4</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
@@ -3405,10 +3399,10 @@
         <v>4</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
@@ -3419,10 +3413,10 @@
         <v>4</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
@@ -3433,10 +3427,10 @@
         <v>4</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
@@ -3447,10 +3441,10 @@
         <v>4</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
@@ -3461,10 +3455,10 @@
         <v>4</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
@@ -3475,10 +3469,10 @@
         <v>4</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
@@ -3489,10 +3483,10 @@
         <v>4</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
@@ -3503,10 +3497,10 @@
         <v>4</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D138" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
@@ -3517,10 +3511,10 @@
         <v>4</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D139" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
@@ -3531,10 +3525,10 @@
         <v>4</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D140" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
@@ -3545,10 +3539,10 @@
         <v>4</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D141" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
@@ -3559,10 +3553,10 @@
         <v>4</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D142" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
@@ -3573,10 +3567,10 @@
         <v>4</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D143" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
@@ -3587,10 +3581,10 @@
         <v>4</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D144" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
@@ -3601,10 +3595,10 @@
         <v>4</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D145" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
@@ -3615,10 +3609,10 @@
         <v>4</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D146" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
@@ -3629,10 +3623,10 @@
         <v>4</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D147" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
@@ -3643,10 +3637,10 @@
         <v>4</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D148" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
@@ -3657,10 +3651,10 @@
         <v>4</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D149" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
@@ -3671,10 +3665,10 @@
         <v>4</v>
       </c>
       <c r="C150" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D150" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
@@ -3685,10 +3679,10 @@
         <v>4</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
@@ -3699,10 +3693,10 @@
         <v>4</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D152" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
@@ -3713,10 +3707,10 @@
         <v>4</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D153" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
@@ -3727,10 +3721,10 @@
         <v>4</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D154" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
@@ -3741,10 +3735,10 @@
         <v>4</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D155" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
@@ -3755,10 +3749,10 @@
         <v>4</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D156" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
@@ -3769,10 +3763,10 @@
         <v>4</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D157" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
@@ -3783,10 +3777,10 @@
         <v>4</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D158" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
@@ -3797,10 +3791,10 @@
         <v>4</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
@@ -3811,10 +3805,10 @@
         <v>4</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
@@ -3825,10 +3819,10 @@
         <v>4</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D161" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
@@ -3839,10 +3833,10 @@
         <v>4</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D162" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
@@ -3853,10 +3847,10 @@
         <v>4</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D163" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
@@ -3867,10 +3861,10 @@
         <v>4</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D164" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
@@ -3881,10 +3875,10 @@
         <v>4</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D165" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
@@ -3895,10 +3889,10 @@
         <v>4</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
@@ -3909,10 +3903,10 @@
         <v>4</v>
       </c>
       <c r="C167" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D167" s="5" t="s">
         <v>176</v>
-      </c>
-      <c r="D167" s="5" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
@@ -3923,10 +3917,10 @@
         <v>4</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
@@ -3937,10 +3931,10 @@
         <v>4</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
@@ -3951,10 +3945,10 @@
         <v>4</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
@@ -3965,10 +3959,10 @@
         <v>4</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D171" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
@@ -3979,10 +3973,10 @@
         <v>4</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
@@ -3993,10 +3987,10 @@
         <v>4</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
@@ -4007,10 +4001,10 @@
         <v>4</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
@@ -4021,10 +4015,10 @@
         <v>4</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
@@ -4035,10 +4029,10 @@
         <v>4</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
@@ -4049,10 +4043,10 @@
         <v>4</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D177" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
@@ -4063,10 +4057,10 @@
         <v>4</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D178" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
@@ -4074,13 +4068,13 @@
         <v>1</v>
       </c>
       <c r="B179" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D179" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="C179" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D179" s="5" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
@@ -4088,13 +4082,13 @@
         <v>2</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D180" s="5" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
@@ -4102,13 +4096,13 @@
         <v>3</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C181" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D181" s="5" t="s">
         <v>192</v>
-      </c>
-      <c r="D181" s="5" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
@@ -4116,13 +4110,13 @@
         <v>4</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D182" s="5" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
@@ -4130,13 +4124,13 @@
         <v>5</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
@@ -4144,13 +4138,13 @@
         <v>6</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
@@ -4158,13 +4152,13 @@
         <v>7</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C185" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D185" s="5" t="s">
         <v>197</v>
-      </c>
-      <c r="D185" s="5" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
@@ -4172,13 +4166,13 @@
         <v>8</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
@@ -4186,13 +4180,13 @@
         <v>9</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
@@ -4200,13 +4194,13 @@
         <v>10</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
@@ -4214,13 +4208,13 @@
         <v>11</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
@@ -4228,13 +4222,13 @@
         <v>12</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
@@ -4242,13 +4236,13 @@
         <v>13</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
@@ -4256,13 +4250,13 @@
         <v>14</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
@@ -4270,13 +4264,13 @@
         <v>15</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
@@ -4284,13 +4278,13 @@
         <v>16</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
@@ -4298,13 +4292,13 @@
         <v>17</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.2">
@@ -4312,13 +4306,13 @@
         <v>18</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
@@ -4326,13 +4320,13 @@
         <v>19</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D197" s="5" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.2">
@@ -4340,13 +4334,13 @@
         <v>20</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D198" s="5" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.2">
@@ -4354,13 +4348,13 @@
         <v>21</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D199" s="5" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
@@ -4368,13 +4362,13 @@
         <v>22</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.2">
@@ -4382,13 +4376,13 @@
         <v>23</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C201" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D201" s="5" t="s">
         <v>214</v>
-      </c>
-      <c r="D201" s="5" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.2">
@@ -4396,13 +4390,13 @@
         <v>24</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D202" s="5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.2">
@@ -4410,13 +4404,13 @@
         <v>25</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D203" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.2">
@@ -4424,13 +4418,13 @@
         <v>26</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D204" s="5" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.2">
@@ -4438,13 +4432,13 @@
         <v>27</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D205" s="5" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.2">
@@ -4452,13 +4446,13 @@
         <v>28</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D206" s="5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.2">
@@ -4466,13 +4460,13 @@
         <v>29</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>189</v>
+        <v>374</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D207" s="5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.2">
@@ -4480,13 +4474,13 @@
         <v>1</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>223</v>
+        <v>375</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D208" s="5" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
@@ -4494,13 +4488,13 @@
         <v>2</v>
       </c>
       <c r="B209" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C209" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D209" s="5" t="s">
         <v>223</v>
-      </c>
-      <c r="C209" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D209" s="5" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
@@ -4508,13 +4502,13 @@
         <v>3</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>223</v>
+        <v>375</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="211" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -4522,13 +4516,13 @@
         <v>4</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>223</v>
+        <v>375</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D211" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
@@ -4536,13 +4530,13 @@
         <v>5</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>223</v>
+        <v>375</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
@@ -4550,13 +4544,13 @@
         <v>6</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>223</v>
+        <v>375</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D213" s="5" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
@@ -4564,13 +4558,13 @@
         <v>7</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>223</v>
+        <v>375</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="D214" s="5" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
@@ -4578,13 +4572,13 @@
         <v>8</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>223</v>
+        <v>375</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D215" s="5" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
@@ -4592,13 +4586,13 @@
         <v>9</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>223</v>
+        <v>375</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
@@ -4606,13 +4600,13 @@
         <v>10</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>237</v>
+        <v>375</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
@@ -4620,13 +4614,13 @@
         <v>11</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>237</v>
+        <v>375</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.2">
@@ -4634,13 +4628,13 @@
         <v>12</v>
       </c>
       <c r="B219" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C219" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D219" s="5" t="s">
         <v>237</v>
-      </c>
-      <c r="C219" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="D219" s="5" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.2">
@@ -4648,13 +4642,13 @@
         <v>1</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.2">
@@ -4662,13 +4656,13 @@
         <v>2</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D221" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.2">
@@ -4676,13 +4670,13 @@
         <v>3</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D222" s="5" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.2">
@@ -4690,13 +4684,13 @@
         <v>4</v>
       </c>
       <c r="B223" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="C223" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D223" s="5" t="s">
         <v>242</v>
-      </c>
-      <c r="C223" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="D223" s="5" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.2">
@@ -4704,13 +4698,13 @@
         <v>1</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>247</v>
+        <v>377</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D224" s="5" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.2">
@@ -4718,13 +4712,13 @@
         <v>2</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>247</v>
+        <v>377</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.2">
@@ -4732,13 +4726,13 @@
         <v>3</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.2">
@@ -4746,13 +4740,13 @@
         <v>4</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>247</v>
+        <v>377</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.2">
@@ -4760,13 +4754,13 @@
         <v>1</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.2">
@@ -4774,13 +4768,13 @@
         <v>2</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.2">
@@ -4788,13 +4782,13 @@
         <v>3</v>
       </c>
       <c r="B230" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="C230" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D230" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="C230" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D230" s="5" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.2">
@@ -4802,13 +4796,13 @@
         <v>4</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.2">
@@ -4816,13 +4810,13 @@
         <v>5</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D232" s="5" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.2">
@@ -4830,13 +4824,13 @@
         <v>6</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C233" s="8" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.2">
@@ -4844,13 +4838,13 @@
         <v>7</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>265</v>
+        <v>376</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="D234" s="5" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.2">
@@ -4858,13 +4852,13 @@
         <v>8</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>265</v>
+        <v>376</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.2">
@@ -4875,10 +4869,10 @@
         <v>4</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.2">
@@ -4889,10 +4883,10 @@
         <v>4</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.2">
@@ -4903,10 +4897,10 @@
         <v>4</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.2">
@@ -4917,10 +4911,10 @@
         <v>4</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.2">
@@ -4931,10 +4925,10 @@
         <v>4</v>
       </c>
       <c r="C240" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="D240" s="6" t="s">
         <v>268</v>
-      </c>
-      <c r="D240" s="6" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
@@ -4945,10 +4939,10 @@
         <v>4</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.2">
@@ -4959,10 +4953,10 @@
         <v>4</v>
       </c>
       <c r="C242" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
@@ -4973,10 +4967,10 @@
         <v>4</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
@@ -4987,10 +4981,10 @@
         <v>4</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
@@ -5001,10 +4995,10 @@
         <v>4</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
@@ -5015,10 +5009,10 @@
         <v>4</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.2">
@@ -5029,10 +5023,10 @@
         <v>4</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.2">
@@ -5043,10 +5037,10 @@
         <v>4</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
@@ -5057,10 +5051,10 @@
         <v>4</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
@@ -5071,10 +5065,10 @@
         <v>4</v>
       </c>
       <c r="C250" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
@@ -5085,10 +5079,10 @@
         <v>4</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D251" s="6" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
@@ -5099,10 +5093,10 @@
         <v>4</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
@@ -5113,10 +5107,10 @@
         <v>4</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
@@ -5127,10 +5121,10 @@
         <v>4</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
@@ -5141,10 +5135,10 @@
         <v>4</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
@@ -5155,10 +5149,10 @@
         <v>4</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.2">
@@ -5169,10 +5163,10 @@
         <v>4</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.2">
@@ -5183,10 +5177,10 @@
         <v>4</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D258" s="6" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.2">
@@ -5197,10 +5191,10 @@
         <v>4</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>293</v>
+        <v>287</v>
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.2">
@@ -5211,10 +5205,10 @@
         <v>4</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.2">
@@ -5225,10 +5219,10 @@
         <v>4</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.2">
@@ -5239,10 +5233,10 @@
         <v>4</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D262" s="6" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.2">
@@ -5253,10 +5247,10 @@
         <v>4</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.2">
@@ -5267,10 +5261,10 @@
         <v>4</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.2">
@@ -5281,10 +5275,10 @@
         <v>4</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.2">
@@ -5295,10 +5289,10 @@
         <v>4</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.2">
@@ -5309,10 +5303,10 @@
         <v>4</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.2">
@@ -5323,10 +5317,10 @@
         <v>4</v>
       </c>
       <c r="C268" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.2">
@@ -5337,10 +5331,10 @@
         <v>4</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.2">
@@ -5351,10 +5345,10 @@
         <v>4</v>
       </c>
       <c r="C270" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D270" s="6" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.2">
@@ -5365,10 +5359,10 @@
         <v>4</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.2">
@@ -5379,10 +5373,10 @@
         <v>4</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D272" s="6" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
@@ -5393,10 +5387,10 @@
         <v>4</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.2">
@@ -5407,10 +5401,10 @@
         <v>4</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
@@ -5421,10 +5415,10 @@
         <v>4</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.2">
@@ -5435,10 +5429,10 @@
         <v>4</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.2">
@@ -5449,10 +5443,10 @@
         <v>4</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D277" s="6" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.2">
@@ -5463,10 +5457,10 @@
         <v>4</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D278" s="6" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.2">
@@ -5477,10 +5471,10 @@
         <v>4</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D279" s="6" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.2">
@@ -5491,10 +5485,10 @@
         <v>4</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.2">
@@ -5505,10 +5499,10 @@
         <v>4</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D281" s="6" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.2">
@@ -5519,10 +5513,10 @@
         <v>4</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.2">
@@ -5533,10 +5527,10 @@
         <v>4</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D283" s="6" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.2">
@@ -5547,10 +5541,10 @@
         <v>4</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.2">
@@ -5561,10 +5555,10 @@
         <v>4</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.2">
@@ -5575,10 +5569,10 @@
         <v>4</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.2">
@@ -5589,10 +5583,10 @@
         <v>4</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D287" s="6" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.2">
@@ -5603,10 +5597,10 @@
         <v>4</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D288" s="6" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.2">
@@ -5617,10 +5611,10 @@
         <v>4</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D289" s="6" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.2">
@@ -5631,10 +5625,10 @@
         <v>4</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.2">
@@ -5645,10 +5639,10 @@
         <v>4</v>
       </c>
       <c r="C291" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D291" s="6" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.2">
@@ -5659,10 +5653,10 @@
         <v>4</v>
       </c>
       <c r="C292" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D292" s="6" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.2">
@@ -5673,10 +5667,10 @@
         <v>4</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D293" s="6" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.2">
@@ -5687,10 +5681,10 @@
         <v>4</v>
       </c>
       <c r="C294" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D294" s="6" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.2">
@@ -5701,10 +5695,10 @@
         <v>4</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.2">
@@ -5715,10 +5709,10 @@
         <v>4</v>
       </c>
       <c r="C296" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D296" s="6" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.2">
@@ -5729,10 +5723,10 @@
         <v>4</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.2">
@@ -5743,10 +5737,10 @@
         <v>4</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D298" s="6" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.2">
@@ -5757,10 +5751,10 @@
         <v>4</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.2">
@@ -5771,10 +5765,10 @@
         <v>4</v>
       </c>
       <c r="C300" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D300" s="6" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.2">
@@ -5785,10 +5779,10 @@
         <v>4</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.2">
@@ -5799,10 +5793,10 @@
         <v>4</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D302" s="6" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.2">
@@ -5813,10 +5807,10 @@
         <v>4</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.2">
@@ -5827,10 +5821,10 @@
         <v>4</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D304" s="6" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.2">
@@ -5841,10 +5835,10 @@
         <v>4</v>
       </c>
       <c r="C305" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D305" s="6" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.2">
@@ -5855,10 +5849,10 @@
         <v>4</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D306" s="6" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.2">
@@ -5869,10 +5863,10 @@
         <v>4</v>
       </c>
       <c r="C307" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D307" s="6" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.2">
@@ -5883,10 +5877,10 @@
         <v>4</v>
       </c>
       <c r="C308" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D308" s="6" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
@@ -5897,10 +5891,10 @@
         <v>4</v>
       </c>
       <c r="C309" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D309" s="6" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.2">
@@ -5911,10 +5905,10 @@
         <v>4</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D310" s="6" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.2">
@@ -5925,10 +5919,10 @@
         <v>4</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D311" s="6" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.2">
@@ -5939,10 +5933,10 @@
         <v>4</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D312" s="6" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.2">
@@ -5953,10 +5947,10 @@
         <v>4</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D313" s="6" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.2">
@@ -5967,10 +5961,10 @@
         <v>4</v>
       </c>
       <c r="C314" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D314" s="6" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.2">
@@ -5981,10 +5975,10 @@
         <v>4</v>
       </c>
       <c r="C315" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D315" s="6" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.2">
@@ -5995,10 +5989,10 @@
         <v>4</v>
       </c>
       <c r="C316" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D316" s="6" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.2">
@@ -6009,10 +6003,10 @@
         <v>4</v>
       </c>
       <c r="C317" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D317" s="6" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.2">
@@ -6023,10 +6017,10 @@
         <v>4</v>
       </c>
       <c r="C318" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D318" s="6" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.2">
@@ -6037,10 +6031,10 @@
         <v>4</v>
       </c>
       <c r="C319" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D319" s="6" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.2">
@@ -6051,10 +6045,10 @@
         <v>4</v>
       </c>
       <c r="C320" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D320" s="6" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.2">
@@ -6065,10 +6059,10 @@
         <v>4</v>
       </c>
       <c r="C321" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D321" s="6" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.2">
@@ -6079,10 +6073,10 @@
         <v>4</v>
       </c>
       <c r="C322" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D322" s="6" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.2">
@@ -6093,10 +6087,10 @@
         <v>4</v>
       </c>
       <c r="C323" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D323" s="6" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.2">
@@ -6107,10 +6101,10 @@
         <v>4</v>
       </c>
       <c r="C324" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D324" s="6" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.2">
@@ -6121,10 +6115,10 @@
         <v>4</v>
       </c>
       <c r="C325" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D325" s="6" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.2">
@@ -6135,10 +6129,10 @@
         <v>4</v>
       </c>
       <c r="C326" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D326" s="6" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.2">
@@ -6149,10 +6143,10 @@
         <v>4</v>
       </c>
       <c r="C327" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D327" s="6" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.2">
@@ -6163,10 +6157,10 @@
         <v>4</v>
       </c>
       <c r="C328" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D328" s="6" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.2">
@@ -6177,10 +6171,10 @@
         <v>4</v>
       </c>
       <c r="C329" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D329" s="6" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.2">
@@ -6191,10 +6185,10 @@
         <v>4</v>
       </c>
       <c r="C330" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D330" s="6" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.2">
@@ -6205,10 +6199,10 @@
         <v>4</v>
       </c>
       <c r="C331" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D331" s="6" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.2">
@@ -6219,10 +6213,10 @@
         <v>4</v>
       </c>
       <c r="C332" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D332" s="6" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.2">
@@ -6233,10 +6227,10 @@
         <v>4</v>
       </c>
       <c r="C333" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D333" s="6" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.2">
@@ -6247,10 +6241,10 @@
         <v>4</v>
       </c>
       <c r="C334" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D334" s="6" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.2">
@@ -6261,10 +6255,10 @@
         <v>4</v>
       </c>
       <c r="C335" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D335" s="6" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.2">
@@ -6275,10 +6269,10 @@
         <v>4</v>
       </c>
       <c r="C336" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D336" s="6" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.2">
@@ -6289,10 +6283,10 @@
         <v>4</v>
       </c>
       <c r="C337" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D337" s="6" t="s">
-        <v>371</v>
+        <v>365</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.2">
@@ -6303,10 +6297,10 @@
         <v>4</v>
       </c>
       <c r="C338" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D338" s="6" t="s">
-        <v>372</v>
+        <v>366</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.2">
@@ -6317,10 +6311,10 @@
         <v>4</v>
       </c>
       <c r="C339" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D339" s="6" t="s">
-        <v>373</v>
+        <v>367</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.2">
@@ -6331,10 +6325,10 @@
         <v>4</v>
       </c>
       <c r="C340" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D340" s="6" t="s">
-        <v>374</v>
+        <v>368</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.2">
@@ -6345,10 +6339,10 @@
         <v>4</v>
       </c>
       <c r="C341" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D341" s="6" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.2">
@@ -6359,10 +6353,10 @@
         <v>4</v>
       </c>
       <c r="C342" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D342" s="6" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.2">
@@ -6373,10 +6367,10 @@
         <v>4</v>
       </c>
       <c r="C343" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D343" s="6" t="s">
-        <v>377</v>
+        <v>371</v>
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.2">
@@ -6387,10 +6381,10 @@
         <v>4</v>
       </c>
       <c r="C344" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D344" s="6" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.2">
@@ -6401,10 +6395,10 @@
         <v>4</v>
       </c>
       <c r="C345" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D345" s="6" t="s">
-        <v>379</v>
+        <v>373</v>
       </c>
     </row>
   </sheetData>

--- a/backend/Vehicle_door_numbers.xlsx
+++ b/backend/Vehicle_door_numbers.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lokesh/IdeaProjects/NTPC_EM/backend/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B5E38E-65F5-124D-B69A-5FAF4D1C8E41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B544215-924F-CA4E-B299-025AFCE5C8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1357" uniqueCount="510">
   <si>
     <t>SL.NO</t>
   </si>
@@ -1159,13 +1159,412 @@
   </si>
   <si>
     <t>Crane</t>
+  </si>
+  <si>
+    <t>CAT-01</t>
+  </si>
+  <si>
+    <t>CAT-02</t>
+  </si>
+  <si>
+    <t>CAT-03</t>
+  </si>
+  <si>
+    <t>EX-01</t>
+  </si>
+  <si>
+    <t>EX-02</t>
+  </si>
+  <si>
+    <t>EX-03</t>
+  </si>
+  <si>
+    <t>EX-04</t>
+  </si>
+  <si>
+    <t>EX-05</t>
+  </si>
+  <si>
+    <t>EX-06</t>
+  </si>
+  <si>
+    <t>EX-07</t>
+  </si>
+  <si>
+    <t>EX-08</t>
+  </si>
+  <si>
+    <t>EX-09</t>
+  </si>
+  <si>
+    <t>EX-10</t>
+  </si>
+  <si>
+    <t>EX-11</t>
+  </si>
+  <si>
+    <t>EX-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX-18 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX-19 </t>
+  </si>
+  <si>
+    <t>EX-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EX-21 </t>
+  </si>
+  <si>
+    <t>EX-13</t>
+  </si>
+  <si>
+    <t>EX-14</t>
+  </si>
+  <si>
+    <t>EX-15</t>
+  </si>
+  <si>
+    <t>EX-16</t>
+  </si>
+  <si>
+    <t>EX-17</t>
+  </si>
+  <si>
+    <t>EX-22</t>
+  </si>
+  <si>
+    <t>EX-23</t>
+  </si>
+  <si>
+    <t>EX-24</t>
+  </si>
+  <si>
+    <t>EX-25</t>
+  </si>
+  <si>
+    <t>EX-26</t>
+  </si>
+  <si>
+    <t>EX-27</t>
+  </si>
+  <si>
+    <t>PC-01</t>
+  </si>
+  <si>
+    <t>PC-02</t>
+  </si>
+  <si>
+    <t>PC-03</t>
+  </si>
+  <si>
+    <t>PC-04</t>
+  </si>
+  <si>
+    <t>PC-05</t>
+  </si>
+  <si>
+    <t>PC-06</t>
+  </si>
+  <si>
+    <t>PC-07</t>
+  </si>
+  <si>
+    <t>PC-08</t>
+  </si>
+  <si>
+    <t>PC-09</t>
+  </si>
+  <si>
+    <t>PC-10</t>
+  </si>
+  <si>
+    <t>PC-20</t>
+  </si>
+  <si>
+    <t>PC-21</t>
+  </si>
+  <si>
+    <t>PC-23</t>
+  </si>
+  <si>
+    <t>PC-26</t>
+  </si>
+  <si>
+    <t>SY 800 (14)</t>
+  </si>
+  <si>
+    <t>D-1</t>
+  </si>
+  <si>
+    <t>D-2</t>
+  </si>
+  <si>
+    <t>D-3</t>
+  </si>
+  <si>
+    <t>D-4</t>
+  </si>
+  <si>
+    <t>D-5</t>
+  </si>
+  <si>
+    <t>D-6</t>
+  </si>
+  <si>
+    <t>D-7</t>
+  </si>
+  <si>
+    <t>D-8</t>
+  </si>
+  <si>
+    <t>D-9</t>
+  </si>
+  <si>
+    <t>D-10</t>
+  </si>
+  <si>
+    <t>D-11</t>
+  </si>
+  <si>
+    <t>D-12</t>
+  </si>
+  <si>
+    <t>D-13</t>
+  </si>
+  <si>
+    <t>D-14(26)</t>
+  </si>
+  <si>
+    <t>D-15(05)</t>
+  </si>
+  <si>
+    <t>D-16(32)</t>
+  </si>
+  <si>
+    <t>D-17(37)</t>
+  </si>
+  <si>
+    <t>D-18(39)</t>
+  </si>
+  <si>
+    <t>D-19(41)</t>
+  </si>
+  <si>
+    <t>D-20(25)</t>
+  </si>
+  <si>
+    <t>D-21(15)</t>
+  </si>
+  <si>
+    <t>D-22(16)</t>
+  </si>
+  <si>
+    <t>GD-01</t>
+  </si>
+  <si>
+    <t>GD-02</t>
+  </si>
+  <si>
+    <t>GD-03</t>
+  </si>
+  <si>
+    <t>GD-04</t>
+  </si>
+  <si>
+    <t>GD-05</t>
+  </si>
+  <si>
+    <t>GD-06</t>
+  </si>
+  <si>
+    <t>GD-09</t>
+  </si>
+  <si>
+    <t>GD-10</t>
+  </si>
+  <si>
+    <t>VL-01</t>
+  </si>
+  <si>
+    <t>VL-02</t>
+  </si>
+  <si>
+    <t>VL-03</t>
+  </si>
+  <si>
+    <t>VL-04</t>
+  </si>
+  <si>
+    <t>VL-05</t>
+  </si>
+  <si>
+    <t>VL-06</t>
+  </si>
+  <si>
+    <t>VL-07</t>
+  </si>
+  <si>
+    <t>ZW-01</t>
+  </si>
+  <si>
+    <t>ZW-02</t>
+  </si>
+  <si>
+    <t>ZW-03</t>
+  </si>
+  <si>
+    <t>LD-03</t>
+  </si>
+  <si>
+    <t>SM-1</t>
+  </si>
+  <si>
+    <t>SM-2</t>
+  </si>
+  <si>
+    <t>SM-3</t>
+  </si>
+  <si>
+    <t>DR-01</t>
+  </si>
+  <si>
+    <t>DR-02</t>
+  </si>
+  <si>
+    <t>DR-03</t>
+  </si>
+  <si>
+    <t>DR-04</t>
+  </si>
+  <si>
+    <t>DR-05</t>
+  </si>
+  <si>
+    <t>DR-06</t>
+  </si>
+  <si>
+    <t>DR-07</t>
+  </si>
+  <si>
+    <t>DR-08</t>
+  </si>
+  <si>
+    <t>DR-09</t>
+  </si>
+  <si>
+    <t>DR-10</t>
+  </si>
+  <si>
+    <t>DR-11</t>
+  </si>
+  <si>
+    <t>Drill Machine</t>
+  </si>
+  <si>
+    <t>ZX470</t>
+  </si>
+  <si>
+    <t>ZX490</t>
+  </si>
+  <si>
+    <t>PC500</t>
+  </si>
+  <si>
+    <t>PC210</t>
+  </si>
+  <si>
+    <t>PC300</t>
+  </si>
+  <si>
+    <t>PC450</t>
+  </si>
+  <si>
+    <t>ZX220LC</t>
+  </si>
+  <si>
+    <t>PC210 LC</t>
+  </si>
+  <si>
+    <t>SY 800HD</t>
+  </si>
+  <si>
+    <t>D155A-6</t>
+  </si>
+  <si>
+    <t>D85Ess-2</t>
+  </si>
+  <si>
+    <t>D85(24000)</t>
+  </si>
+  <si>
+    <t>D85(30612)</t>
+  </si>
+  <si>
+    <t>D85 (10000)</t>
+  </si>
+  <si>
+    <t>D85(20000)</t>
+  </si>
+  <si>
+    <t>D85(17916)</t>
+  </si>
+  <si>
+    <t>D85(14941)</t>
+  </si>
+  <si>
+    <t>D85(9962)</t>
+  </si>
+  <si>
+    <t>D85(19971)</t>
+  </si>
+  <si>
+    <t>D85(22628)</t>
+  </si>
+  <si>
+    <t>GD705-5</t>
+  </si>
+  <si>
+    <t>L150H</t>
+  </si>
+  <si>
+    <t>ZW225-6</t>
+  </si>
+  <si>
+    <t>L&amp;T 9020</t>
+  </si>
+  <si>
+    <t>SM220</t>
+  </si>
+  <si>
+    <t>HITACHI 210</t>
+  </si>
+  <si>
+    <t>Excavator</t>
+  </si>
+  <si>
+    <t>Dozer</t>
+  </si>
+  <si>
+    <t>Grader</t>
+  </si>
+  <si>
+    <t>Wheel Loader</t>
+  </si>
+  <si>
+    <t>Surface Miner</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$]dd/mm/yyyy;@"/>
+  </numFmts>
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1204,6 +1603,24 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1254,7 +1671,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1288,6 +1705,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1570,7 +2005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D345"/>
+  <dimension ref="A1:D454"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.5" style="9" customWidth="1"/>
@@ -4064,8 +4499,8 @@
       </c>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A179" s="2">
-        <v>1</v>
+      <c r="A179" s="1">
+        <v>177</v>
       </c>
       <c r="B179" s="2" t="s">
         <v>374</v>
@@ -4078,8 +4513,8 @@
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A180" s="2">
-        <v>2</v>
+      <c r="A180" s="1">
+        <v>178</v>
       </c>
       <c r="B180" s="2" t="s">
         <v>374</v>
@@ -4092,8 +4527,8 @@
       </c>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A181" s="2">
-        <v>3</v>
+      <c r="A181" s="1">
+        <v>179</v>
       </c>
       <c r="B181" s="2" t="s">
         <v>374</v>
@@ -4106,8 +4541,8 @@
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A182" s="2">
-        <v>4</v>
+      <c r="A182" s="1">
+        <v>180</v>
       </c>
       <c r="B182" s="2" t="s">
         <v>374</v>
@@ -4120,8 +4555,8 @@
       </c>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A183" s="2">
-        <v>5</v>
+      <c r="A183" s="1">
+        <v>181</v>
       </c>
       <c r="B183" s="2" t="s">
         <v>374</v>
@@ -4134,8 +4569,8 @@
       </c>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A184" s="2">
-        <v>6</v>
+      <c r="A184" s="1">
+        <v>182</v>
       </c>
       <c r="B184" s="2" t="s">
         <v>374</v>
@@ -4148,8 +4583,8 @@
       </c>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A185" s="2">
-        <v>7</v>
+      <c r="A185" s="1">
+        <v>183</v>
       </c>
       <c r="B185" s="2" t="s">
         <v>374</v>
@@ -4162,8 +4597,8 @@
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A186" s="2">
-        <v>8</v>
+      <c r="A186" s="1">
+        <v>184</v>
       </c>
       <c r="B186" s="2" t="s">
         <v>374</v>
@@ -4176,8 +4611,8 @@
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A187" s="2">
-        <v>9</v>
+      <c r="A187" s="1">
+        <v>185</v>
       </c>
       <c r="B187" s="2" t="s">
         <v>374</v>
@@ -4190,8 +4625,8 @@
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A188" s="2">
-        <v>10</v>
+      <c r="A188" s="1">
+        <v>186</v>
       </c>
       <c r="B188" s="2" t="s">
         <v>374</v>
@@ -4204,8 +4639,8 @@
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A189" s="2">
-        <v>11</v>
+      <c r="A189" s="1">
+        <v>187</v>
       </c>
       <c r="B189" s="2" t="s">
         <v>374</v>
@@ -4218,8 +4653,8 @@
       </c>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A190" s="2">
-        <v>12</v>
+      <c r="A190" s="1">
+        <v>188</v>
       </c>
       <c r="B190" s="2" t="s">
         <v>374</v>
@@ -4232,8 +4667,8 @@
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A191" s="2">
-        <v>13</v>
+      <c r="A191" s="1">
+        <v>189</v>
       </c>
       <c r="B191" s="2" t="s">
         <v>374</v>
@@ -4246,8 +4681,8 @@
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A192" s="2">
-        <v>14</v>
+      <c r="A192" s="1">
+        <v>190</v>
       </c>
       <c r="B192" s="2" t="s">
         <v>374</v>
@@ -4260,8 +4695,8 @@
       </c>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A193" s="2">
-        <v>15</v>
+      <c r="A193" s="1">
+        <v>191</v>
       </c>
       <c r="B193" s="2" t="s">
         <v>374</v>
@@ -4274,8 +4709,8 @@
       </c>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A194" s="2">
-        <v>16</v>
+      <c r="A194" s="1">
+        <v>192</v>
       </c>
       <c r="B194" s="2" t="s">
         <v>374</v>
@@ -4288,8 +4723,8 @@
       </c>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A195" s="2">
-        <v>17</v>
+      <c r="A195" s="1">
+        <v>193</v>
       </c>
       <c r="B195" s="2" t="s">
         <v>374</v>
@@ -4302,8 +4737,8 @@
       </c>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A196" s="2">
-        <v>18</v>
+      <c r="A196" s="1">
+        <v>194</v>
       </c>
       <c r="B196" s="2" t="s">
         <v>374</v>
@@ -4316,8 +4751,8 @@
       </c>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A197" s="2">
-        <v>19</v>
+      <c r="A197" s="1">
+        <v>195</v>
       </c>
       <c r="B197" s="2" t="s">
         <v>374</v>
@@ -4330,8 +4765,8 @@
       </c>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A198" s="2">
-        <v>20</v>
+      <c r="A198" s="1">
+        <v>196</v>
       </c>
       <c r="B198" s="2" t="s">
         <v>374</v>
@@ -4344,8 +4779,8 @@
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A199" s="2">
-        <v>21</v>
+      <c r="A199" s="1">
+        <v>197</v>
       </c>
       <c r="B199" s="2" t="s">
         <v>374</v>
@@ -4358,8 +4793,8 @@
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A200" s="2">
-        <v>22</v>
+      <c r="A200" s="1">
+        <v>198</v>
       </c>
       <c r="B200" s="2" t="s">
         <v>374</v>
@@ -4372,8 +4807,8 @@
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A201" s="2">
-        <v>23</v>
+      <c r="A201" s="1">
+        <v>199</v>
       </c>
       <c r="B201" s="2" t="s">
         <v>374</v>
@@ -4386,8 +4821,8 @@
       </c>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A202" s="2">
-        <v>24</v>
+      <c r="A202" s="1">
+        <v>200</v>
       </c>
       <c r="B202" s="2" t="s">
         <v>374</v>
@@ -4400,8 +4835,8 @@
       </c>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A203" s="2">
-        <v>25</v>
+      <c r="A203" s="1">
+        <v>201</v>
       </c>
       <c r="B203" s="2" t="s">
         <v>374</v>
@@ -4414,8 +4849,8 @@
       </c>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A204" s="2">
-        <v>26</v>
+      <c r="A204" s="1">
+        <v>202</v>
       </c>
       <c r="B204" s="2" t="s">
         <v>374</v>
@@ -4428,8 +4863,8 @@
       </c>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A205" s="2">
-        <v>27</v>
+      <c r="A205" s="1">
+        <v>203</v>
       </c>
       <c r="B205" s="2" t="s">
         <v>374</v>
@@ -4442,8 +4877,8 @@
       </c>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A206" s="2">
-        <v>28</v>
+      <c r="A206" s="1">
+        <v>204</v>
       </c>
       <c r="B206" s="2" t="s">
         <v>374</v>
@@ -4456,8 +4891,8 @@
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A207" s="2">
-        <v>29</v>
+      <c r="A207" s="1">
+        <v>205</v>
       </c>
       <c r="B207" s="2" t="s">
         <v>374</v>
@@ -4470,8 +4905,8 @@
       </c>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A208" s="2">
-        <v>1</v>
+      <c r="A208" s="1">
+        <v>206</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>375</v>
@@ -4484,8 +4919,8 @@
       </c>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A209" s="2">
-        <v>2</v>
+      <c r="A209" s="1">
+        <v>207</v>
       </c>
       <c r="B209" s="2" t="s">
         <v>375</v>
@@ -4498,8 +4933,8 @@
       </c>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A210" s="2">
-        <v>3</v>
+      <c r="A210" s="1">
+        <v>208</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>375</v>
@@ -4512,8 +4947,8 @@
       </c>
     </row>
     <row r="211" spans="1:4" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="2">
-        <v>4</v>
+      <c r="A211" s="1">
+        <v>209</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>375</v>
@@ -4526,8 +4961,8 @@
       </c>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A212" s="2">
-        <v>5</v>
+      <c r="A212" s="1">
+        <v>210</v>
       </c>
       <c r="B212" s="2" t="s">
         <v>375</v>
@@ -4540,8 +4975,8 @@
       </c>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A213" s="2">
-        <v>6</v>
+      <c r="A213" s="1">
+        <v>211</v>
       </c>
       <c r="B213" s="2" t="s">
         <v>375</v>
@@ -4554,8 +4989,8 @@
       </c>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A214" s="2">
-        <v>7</v>
+      <c r="A214" s="1">
+        <v>212</v>
       </c>
       <c r="B214" s="2" t="s">
         <v>375</v>
@@ -4568,8 +5003,8 @@
       </c>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A215" s="2">
-        <v>8</v>
+      <c r="A215" s="1">
+        <v>213</v>
       </c>
       <c r="B215" s="2" t="s">
         <v>375</v>
@@ -4582,8 +5017,8 @@
       </c>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A216" s="2">
-        <v>9</v>
+      <c r="A216" s="1">
+        <v>214</v>
       </c>
       <c r="B216" s="2" t="s">
         <v>375</v>
@@ -4596,8 +5031,8 @@
       </c>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A217" s="2">
-        <v>10</v>
+      <c r="A217" s="1">
+        <v>215</v>
       </c>
       <c r="B217" s="2" t="s">
         <v>375</v>
@@ -4610,8 +5045,8 @@
       </c>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A218" s="2">
-        <v>11</v>
+      <c r="A218" s="1">
+        <v>216</v>
       </c>
       <c r="B218" s="2" t="s">
         <v>375</v>
@@ -4624,8 +5059,8 @@
       </c>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A219" s="2">
-        <v>12</v>
+      <c r="A219" s="1">
+        <v>217</v>
       </c>
       <c r="B219" s="2" t="s">
         <v>375</v>
@@ -4638,8 +5073,8 @@
       </c>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A220" s="2">
-        <v>1</v>
+      <c r="A220" s="1">
+        <v>218</v>
       </c>
       <c r="B220" s="2" t="s">
         <v>238</v>
@@ -4652,8 +5087,8 @@
       </c>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A221" s="2">
-        <v>2</v>
+      <c r="A221" s="1">
+        <v>219</v>
       </c>
       <c r="B221" s="2" t="s">
         <v>238</v>
@@ -4666,8 +5101,8 @@
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A222" s="2">
-        <v>3</v>
+      <c r="A222" s="1">
+        <v>220</v>
       </c>
       <c r="B222" s="2" t="s">
         <v>238</v>
@@ -4680,8 +5115,8 @@
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A223" s="2">
-        <v>4</v>
+      <c r="A223" s="1">
+        <v>221</v>
       </c>
       <c r="B223" s="2" t="s">
         <v>238</v>
@@ -4694,8 +5129,8 @@
       </c>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A224" s="2">
-        <v>1</v>
+      <c r="A224" s="1">
+        <v>222</v>
       </c>
       <c r="B224" s="2" t="s">
         <v>377</v>
@@ -4708,8 +5143,8 @@
       </c>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A225" s="2">
-        <v>2</v>
+      <c r="A225" s="1">
+        <v>223</v>
       </c>
       <c r="B225" s="2" t="s">
         <v>377</v>
@@ -4722,8 +5157,8 @@
       </c>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A226" s="2">
-        <v>3</v>
+      <c r="A226" s="1">
+        <v>224</v>
       </c>
       <c r="B226" s="2" t="s">
         <v>246</v>
@@ -4736,8 +5171,8 @@
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A227" s="2">
-        <v>4</v>
+      <c r="A227" s="1">
+        <v>225</v>
       </c>
       <c r="B227" s="2" t="s">
         <v>377</v>
@@ -4750,8 +5185,8 @@
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A228" s="2">
-        <v>1</v>
+      <c r="A228" s="1">
+        <v>226</v>
       </c>
       <c r="B228" s="2" t="s">
         <v>250</v>
@@ -4764,8 +5199,8 @@
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A229" s="2">
-        <v>2</v>
+      <c r="A229" s="1">
+        <v>227</v>
       </c>
       <c r="B229" s="2" t="s">
         <v>250</v>
@@ -4778,8 +5213,8 @@
       </c>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A230" s="2">
-        <v>3</v>
+      <c r="A230" s="1">
+        <v>228</v>
       </c>
       <c r="B230" s="2" t="s">
         <v>250</v>
@@ -4792,8 +5227,8 @@
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A231" s="2">
-        <v>4</v>
+      <c r="A231" s="1">
+        <v>229</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>250</v>
@@ -4806,8 +5241,8 @@
       </c>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A232" s="2">
-        <v>5</v>
+      <c r="A232" s="1">
+        <v>230</v>
       </c>
       <c r="B232" s="2" t="s">
         <v>250</v>
@@ -4820,8 +5255,8 @@
       </c>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A233" s="2">
-        <v>6</v>
+      <c r="A233" s="1">
+        <v>231</v>
       </c>
       <c r="B233" s="2" t="s">
         <v>250</v>
@@ -4834,8 +5269,8 @@
       </c>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A234" s="2">
-        <v>7</v>
+      <c r="A234" s="1">
+        <v>232</v>
       </c>
       <c r="B234" s="2" t="s">
         <v>376</v>
@@ -4848,8 +5283,8 @@
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A235" s="2">
-        <v>8</v>
+      <c r="A235" s="1">
+        <v>233</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>376</v>
@@ -4862,8 +5297,8 @@
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A236" s="6">
-        <v>1</v>
+      <c r="A236" s="1">
+        <v>234</v>
       </c>
       <c r="B236" s="2" t="s">
         <v>4</v>
@@ -4876,8 +5311,8 @@
       </c>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A237" s="6">
-        <v>2</v>
+      <c r="A237" s="1">
+        <v>235</v>
       </c>
       <c r="B237" s="2" t="s">
         <v>4</v>
@@ -4890,8 +5325,8 @@
       </c>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A238" s="6">
-        <v>3</v>
+      <c r="A238" s="1">
+        <v>236</v>
       </c>
       <c r="B238" s="2" t="s">
         <v>4</v>
@@ -4904,8 +5339,8 @@
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A239" s="6">
-        <v>4</v>
+      <c r="A239" s="1">
+        <v>237</v>
       </c>
       <c r="B239" s="2" t="s">
         <v>4</v>
@@ -4918,8 +5353,8 @@
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A240" s="6">
-        <v>5</v>
+      <c r="A240" s="1">
+        <v>238</v>
       </c>
       <c r="B240" s="2" t="s">
         <v>4</v>
@@ -4932,8 +5367,8 @@
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A241" s="6">
-        <v>6</v>
+      <c r="A241" s="1">
+        <v>239</v>
       </c>
       <c r="B241" s="2" t="s">
         <v>4</v>
@@ -4946,8 +5381,8 @@
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A242" s="6">
-        <v>7</v>
+      <c r="A242" s="1">
+        <v>240</v>
       </c>
       <c r="B242" s="2" t="s">
         <v>4</v>
@@ -4960,8 +5395,8 @@
       </c>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A243" s="6">
-        <v>8</v>
+      <c r="A243" s="1">
+        <v>241</v>
       </c>
       <c r="B243" s="2" t="s">
         <v>4</v>
@@ -4974,8 +5409,8 @@
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A244" s="6">
-        <v>9</v>
+      <c r="A244" s="1">
+        <v>242</v>
       </c>
       <c r="B244" s="2" t="s">
         <v>4</v>
@@ -4988,8 +5423,8 @@
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A245" s="6">
-        <v>10</v>
+      <c r="A245" s="1">
+        <v>243</v>
       </c>
       <c r="B245" s="2" t="s">
         <v>4</v>
@@ -5002,8 +5437,8 @@
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A246" s="6">
-        <v>11</v>
+      <c r="A246" s="1">
+        <v>244</v>
       </c>
       <c r="B246" s="2" t="s">
         <v>4</v>
@@ -5016,8 +5451,8 @@
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A247" s="6">
-        <v>12</v>
+      <c r="A247" s="1">
+        <v>245</v>
       </c>
       <c r="B247" s="2" t="s">
         <v>4</v>
@@ -5030,8 +5465,8 @@
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A248" s="6">
-        <v>13</v>
+      <c r="A248" s="1">
+        <v>246</v>
       </c>
       <c r="B248" s="2" t="s">
         <v>4</v>
@@ -5044,8 +5479,8 @@
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A249" s="6">
-        <v>14</v>
+      <c r="A249" s="1">
+        <v>247</v>
       </c>
       <c r="B249" s="2" t="s">
         <v>4</v>
@@ -5058,8 +5493,8 @@
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A250" s="6">
-        <v>15</v>
+      <c r="A250" s="1">
+        <v>248</v>
       </c>
       <c r="B250" s="2" t="s">
         <v>4</v>
@@ -5072,8 +5507,8 @@
       </c>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A251" s="6">
-        <v>16</v>
+      <c r="A251" s="1">
+        <v>249</v>
       </c>
       <c r="B251" s="2" t="s">
         <v>4</v>
@@ -5086,8 +5521,8 @@
       </c>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A252" s="6">
-        <v>17</v>
+      <c r="A252" s="1">
+        <v>250</v>
       </c>
       <c r="B252" s="2" t="s">
         <v>4</v>
@@ -5100,8 +5535,8 @@
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A253" s="6">
-        <v>18</v>
+      <c r="A253" s="1">
+        <v>251</v>
       </c>
       <c r="B253" s="2" t="s">
         <v>4</v>
@@ -5114,8 +5549,8 @@
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A254" s="6">
-        <v>19</v>
+      <c r="A254" s="1">
+        <v>252</v>
       </c>
       <c r="B254" s="2" t="s">
         <v>4</v>
@@ -5128,8 +5563,8 @@
       </c>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A255" s="6">
-        <v>20</v>
+      <c r="A255" s="1">
+        <v>253</v>
       </c>
       <c r="B255" s="2" t="s">
         <v>4</v>
@@ -5142,8 +5577,8 @@
       </c>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A256" s="6">
-        <v>21</v>
+      <c r="A256" s="1">
+        <v>254</v>
       </c>
       <c r="B256" s="2" t="s">
         <v>4</v>
@@ -5156,8 +5591,8 @@
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A257" s="6">
-        <v>22</v>
+      <c r="A257" s="1">
+        <v>255</v>
       </c>
       <c r="B257" s="2" t="s">
         <v>4</v>
@@ -5170,8 +5605,8 @@
       </c>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A258" s="6">
-        <v>23</v>
+      <c r="A258" s="1">
+        <v>256</v>
       </c>
       <c r="B258" s="2" t="s">
         <v>4</v>
@@ -5184,8 +5619,8 @@
       </c>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A259" s="6">
-        <v>24</v>
+      <c r="A259" s="1">
+        <v>257</v>
       </c>
       <c r="B259" s="2" t="s">
         <v>4</v>
@@ -5198,8 +5633,8 @@
       </c>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A260" s="6">
-        <v>25</v>
+      <c r="A260" s="1">
+        <v>258</v>
       </c>
       <c r="B260" s="2" t="s">
         <v>4</v>
@@ -5212,8 +5647,8 @@
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A261" s="6">
-        <v>26</v>
+      <c r="A261" s="1">
+        <v>259</v>
       </c>
       <c r="B261" s="2" t="s">
         <v>4</v>
@@ -5226,8 +5661,8 @@
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A262" s="6">
-        <v>27</v>
+      <c r="A262" s="1">
+        <v>260</v>
       </c>
       <c r="B262" s="2" t="s">
         <v>4</v>
@@ -5240,8 +5675,8 @@
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A263" s="6">
-        <v>28</v>
+      <c r="A263" s="1">
+        <v>261</v>
       </c>
       <c r="B263" s="2" t="s">
         <v>4</v>
@@ -5254,8 +5689,8 @@
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A264" s="6">
-        <v>29</v>
+      <c r="A264" s="1">
+        <v>262</v>
       </c>
       <c r="B264" s="2" t="s">
         <v>4</v>
@@ -5268,8 +5703,8 @@
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A265" s="6">
-        <v>30</v>
+      <c r="A265" s="1">
+        <v>263</v>
       </c>
       <c r="B265" s="2" t="s">
         <v>4</v>
@@ -5282,8 +5717,8 @@
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A266" s="6">
-        <v>31</v>
+      <c r="A266" s="1">
+        <v>264</v>
       </c>
       <c r="B266" s="2" t="s">
         <v>4</v>
@@ -5296,8 +5731,8 @@
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A267" s="6">
-        <v>32</v>
+      <c r="A267" s="1">
+        <v>265</v>
       </c>
       <c r="B267" s="2" t="s">
         <v>4</v>
@@ -5310,8 +5745,8 @@
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A268" s="6">
-        <v>33</v>
+      <c r="A268" s="1">
+        <v>266</v>
       </c>
       <c r="B268" s="2" t="s">
         <v>4</v>
@@ -5324,8 +5759,8 @@
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A269" s="6">
-        <v>34</v>
+      <c r="A269" s="1">
+        <v>267</v>
       </c>
       <c r="B269" s="2" t="s">
         <v>4</v>
@@ -5338,8 +5773,8 @@
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A270" s="6">
-        <v>35</v>
+      <c r="A270" s="1">
+        <v>268</v>
       </c>
       <c r="B270" s="2" t="s">
         <v>4</v>
@@ -5352,8 +5787,8 @@
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A271" s="6">
-        <v>36</v>
+      <c r="A271" s="1">
+        <v>269</v>
       </c>
       <c r="B271" s="2" t="s">
         <v>4</v>
@@ -5366,8 +5801,8 @@
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A272" s="6">
-        <v>37</v>
+      <c r="A272" s="1">
+        <v>270</v>
       </c>
       <c r="B272" s="2" t="s">
         <v>4</v>
@@ -5380,8 +5815,8 @@
       </c>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A273" s="6">
-        <v>38</v>
+      <c r="A273" s="1">
+        <v>271</v>
       </c>
       <c r="B273" s="2" t="s">
         <v>4</v>
@@ -5394,8 +5829,8 @@
       </c>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A274" s="6">
-        <v>39</v>
+      <c r="A274" s="1">
+        <v>272</v>
       </c>
       <c r="B274" s="2" t="s">
         <v>4</v>
@@ -5408,8 +5843,8 @@
       </c>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A275" s="6">
-        <v>40</v>
+      <c r="A275" s="1">
+        <v>273</v>
       </c>
       <c r="B275" s="2" t="s">
         <v>4</v>
@@ -5422,8 +5857,8 @@
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A276" s="6">
-        <v>41</v>
+      <c r="A276" s="1">
+        <v>274</v>
       </c>
       <c r="B276" s="2" t="s">
         <v>4</v>
@@ -5436,8 +5871,8 @@
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A277" s="6">
-        <v>42</v>
+      <c r="A277" s="1">
+        <v>275</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>4</v>
@@ -5450,8 +5885,8 @@
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A278" s="6">
-        <v>43</v>
+      <c r="A278" s="1">
+        <v>276</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>4</v>
@@ -5464,8 +5899,8 @@
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A279" s="6">
-        <v>44</v>
+      <c r="A279" s="1">
+        <v>277</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>4</v>
@@ -5478,8 +5913,8 @@
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A280" s="6">
-        <v>45</v>
+      <c r="A280" s="1">
+        <v>278</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>4</v>
@@ -5492,8 +5927,8 @@
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A281" s="6">
-        <v>46</v>
+      <c r="A281" s="1">
+        <v>279</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>4</v>
@@ -5506,8 +5941,8 @@
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A282" s="6">
-        <v>47</v>
+      <c r="A282" s="1">
+        <v>280</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>4</v>
@@ -5520,8 +5955,8 @@
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A283" s="6">
-        <v>48</v>
+      <c r="A283" s="1">
+        <v>281</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>4</v>
@@ -5534,8 +5969,8 @@
       </c>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A284" s="6">
-        <v>49</v>
+      <c r="A284" s="1">
+        <v>282</v>
       </c>
       <c r="B284" s="2" t="s">
         <v>4</v>
@@ -5548,8 +5983,8 @@
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A285" s="6">
-        <v>50</v>
+      <c r="A285" s="1">
+        <v>283</v>
       </c>
       <c r="B285" s="2" t="s">
         <v>4</v>
@@ -5562,8 +5997,8 @@
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A286" s="6">
-        <v>51</v>
+      <c r="A286" s="1">
+        <v>284</v>
       </c>
       <c r="B286" s="2" t="s">
         <v>4</v>
@@ -5576,8 +6011,8 @@
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A287" s="6">
-        <v>52</v>
+      <c r="A287" s="1">
+        <v>285</v>
       </c>
       <c r="B287" s="2" t="s">
         <v>4</v>
@@ -5590,8 +6025,8 @@
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A288" s="6">
-        <v>53</v>
+      <c r="A288" s="1">
+        <v>286</v>
       </c>
       <c r="B288" s="2" t="s">
         <v>4</v>
@@ -5604,8 +6039,8 @@
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A289" s="6">
-        <v>54</v>
+      <c r="A289" s="1">
+        <v>287</v>
       </c>
       <c r="B289" s="2" t="s">
         <v>4</v>
@@ -5618,8 +6053,8 @@
       </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A290" s="6">
-        <v>55</v>
+      <c r="A290" s="1">
+        <v>288</v>
       </c>
       <c r="B290" s="2" t="s">
         <v>4</v>
@@ -5632,8 +6067,8 @@
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A291" s="6">
-        <v>56</v>
+      <c r="A291" s="1">
+        <v>289</v>
       </c>
       <c r="B291" s="2" t="s">
         <v>4</v>
@@ -5646,8 +6081,8 @@
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A292" s="6">
-        <v>57</v>
+      <c r="A292" s="1">
+        <v>290</v>
       </c>
       <c r="B292" s="2" t="s">
         <v>4</v>
@@ -5660,8 +6095,8 @@
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A293" s="6">
-        <v>58</v>
+      <c r="A293" s="1">
+        <v>291</v>
       </c>
       <c r="B293" s="2" t="s">
         <v>4</v>
@@ -5674,8 +6109,8 @@
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A294" s="6">
-        <v>59</v>
+      <c r="A294" s="1">
+        <v>292</v>
       </c>
       <c r="B294" s="2" t="s">
         <v>4</v>
@@ -5688,8 +6123,8 @@
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A295" s="6">
-        <v>60</v>
+      <c r="A295" s="1">
+        <v>293</v>
       </c>
       <c r="B295" s="2" t="s">
         <v>4</v>
@@ -5702,8 +6137,8 @@
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A296" s="6">
-        <v>61</v>
+      <c r="A296" s="1">
+        <v>294</v>
       </c>
       <c r="B296" s="2" t="s">
         <v>4</v>
@@ -5716,8 +6151,8 @@
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A297" s="6">
-        <v>62</v>
+      <c r="A297" s="1">
+        <v>295</v>
       </c>
       <c r="B297" s="2" t="s">
         <v>4</v>
@@ -5730,8 +6165,8 @@
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A298" s="6">
-        <v>63</v>
+      <c r="A298" s="1">
+        <v>296</v>
       </c>
       <c r="B298" s="2" t="s">
         <v>4</v>
@@ -5744,8 +6179,8 @@
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A299" s="6">
-        <v>64</v>
+      <c r="A299" s="1">
+        <v>297</v>
       </c>
       <c r="B299" s="2" t="s">
         <v>4</v>
@@ -5758,8 +6193,8 @@
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A300" s="6">
-        <v>65</v>
+      <c r="A300" s="1">
+        <v>298</v>
       </c>
       <c r="B300" s="2" t="s">
         <v>4</v>
@@ -5772,8 +6207,8 @@
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A301" s="6">
-        <v>66</v>
+      <c r="A301" s="1">
+        <v>299</v>
       </c>
       <c r="B301" s="2" t="s">
         <v>4</v>
@@ -5786,8 +6221,8 @@
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A302" s="6">
-        <v>67</v>
+      <c r="A302" s="1">
+        <v>300</v>
       </c>
       <c r="B302" s="2" t="s">
         <v>4</v>
@@ -5800,8 +6235,8 @@
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A303" s="6">
-        <v>68</v>
+      <c r="A303" s="1">
+        <v>301</v>
       </c>
       <c r="B303" s="2" t="s">
         <v>4</v>
@@ -5814,8 +6249,8 @@
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A304" s="6">
-        <v>69</v>
+      <c r="A304" s="1">
+        <v>302</v>
       </c>
       <c r="B304" s="2" t="s">
         <v>4</v>
@@ -5828,8 +6263,8 @@
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A305" s="6">
-        <v>70</v>
+      <c r="A305" s="1">
+        <v>303</v>
       </c>
       <c r="B305" s="2" t="s">
         <v>4</v>
@@ -5842,8 +6277,8 @@
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A306" s="6">
-        <v>71</v>
+      <c r="A306" s="1">
+        <v>304</v>
       </c>
       <c r="B306" s="2" t="s">
         <v>4</v>
@@ -5856,8 +6291,8 @@
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A307" s="6">
-        <v>72</v>
+      <c r="A307" s="1">
+        <v>305</v>
       </c>
       <c r="B307" s="2" t="s">
         <v>4</v>
@@ -5870,8 +6305,8 @@
       </c>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A308" s="6">
-        <v>73</v>
+      <c r="A308" s="1">
+        <v>306</v>
       </c>
       <c r="B308" s="2" t="s">
         <v>4</v>
@@ -5884,8 +6319,8 @@
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A309" s="6">
-        <v>74</v>
+      <c r="A309" s="1">
+        <v>307</v>
       </c>
       <c r="B309" s="2" t="s">
         <v>4</v>
@@ -5898,8 +6333,8 @@
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A310" s="6">
-        <v>75</v>
+      <c r="A310" s="1">
+        <v>308</v>
       </c>
       <c r="B310" s="2" t="s">
         <v>4</v>
@@ -5912,8 +6347,8 @@
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A311" s="6">
-        <v>76</v>
+      <c r="A311" s="1">
+        <v>309</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>4</v>
@@ -5926,8 +6361,8 @@
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A312" s="6">
-        <v>77</v>
+      <c r="A312" s="1">
+        <v>310</v>
       </c>
       <c r="B312" s="2" t="s">
         <v>4</v>
@@ -5940,8 +6375,8 @@
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A313" s="6">
-        <v>78</v>
+      <c r="A313" s="1">
+        <v>311</v>
       </c>
       <c r="B313" s="2" t="s">
         <v>4</v>
@@ -5954,8 +6389,8 @@
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A314" s="6">
-        <v>79</v>
+      <c r="A314" s="1">
+        <v>312</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>4</v>
@@ -5968,8 +6403,8 @@
       </c>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A315" s="6">
-        <v>80</v>
+      <c r="A315" s="1">
+        <v>313</v>
       </c>
       <c r="B315" s="2" t="s">
         <v>4</v>
@@ -5982,8 +6417,8 @@
       </c>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A316" s="6">
-        <v>81</v>
+      <c r="A316" s="1">
+        <v>314</v>
       </c>
       <c r="B316" s="2" t="s">
         <v>4</v>
@@ -5996,8 +6431,8 @@
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A317" s="6">
-        <v>82</v>
+      <c r="A317" s="1">
+        <v>315</v>
       </c>
       <c r="B317" s="2" t="s">
         <v>4</v>
@@ -6010,8 +6445,8 @@
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A318" s="6">
-        <v>83</v>
+      <c r="A318" s="1">
+        <v>316</v>
       </c>
       <c r="B318" s="2" t="s">
         <v>4</v>
@@ -6024,8 +6459,8 @@
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A319" s="6">
-        <v>84</v>
+      <c r="A319" s="1">
+        <v>317</v>
       </c>
       <c r="B319" s="2" t="s">
         <v>4</v>
@@ -6038,8 +6473,8 @@
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A320" s="6">
-        <v>85</v>
+      <c r="A320" s="1">
+        <v>318</v>
       </c>
       <c r="B320" s="2" t="s">
         <v>4</v>
@@ -6052,8 +6487,8 @@
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A321" s="6">
-        <v>86</v>
+      <c r="A321" s="1">
+        <v>319</v>
       </c>
       <c r="B321" s="2" t="s">
         <v>4</v>
@@ -6066,8 +6501,8 @@
       </c>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A322" s="6">
-        <v>87</v>
+      <c r="A322" s="1">
+        <v>320</v>
       </c>
       <c r="B322" s="2" t="s">
         <v>4</v>
@@ -6080,8 +6515,8 @@
       </c>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A323" s="6">
-        <v>88</v>
+      <c r="A323" s="1">
+        <v>321</v>
       </c>
       <c r="B323" s="2" t="s">
         <v>4</v>
@@ -6094,8 +6529,8 @@
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A324" s="6">
-        <v>89</v>
+      <c r="A324" s="1">
+        <v>322</v>
       </c>
       <c r="B324" s="2" t="s">
         <v>4</v>
@@ -6108,8 +6543,8 @@
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A325" s="6">
-        <v>90</v>
+      <c r="A325" s="1">
+        <v>323</v>
       </c>
       <c r="B325" s="2" t="s">
         <v>4</v>
@@ -6122,8 +6557,8 @@
       </c>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A326" s="6">
-        <v>91</v>
+      <c r="A326" s="1">
+        <v>324</v>
       </c>
       <c r="B326" s="2" t="s">
         <v>4</v>
@@ -6136,8 +6571,8 @@
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A327" s="6">
-        <v>92</v>
+      <c r="A327" s="1">
+        <v>325</v>
       </c>
       <c r="B327" s="2" t="s">
         <v>4</v>
@@ -6150,8 +6585,8 @@
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A328" s="6">
-        <v>93</v>
+      <c r="A328" s="1">
+        <v>326</v>
       </c>
       <c r="B328" s="2" t="s">
         <v>4</v>
@@ -6164,8 +6599,8 @@
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A329" s="6">
-        <v>94</v>
+      <c r="A329" s="1">
+        <v>327</v>
       </c>
       <c r="B329" s="2" t="s">
         <v>4</v>
@@ -6178,8 +6613,8 @@
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A330" s="6">
-        <v>95</v>
+      <c r="A330" s="1">
+        <v>328</v>
       </c>
       <c r="B330" s="2" t="s">
         <v>4</v>
@@ -6192,8 +6627,8 @@
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A331" s="6">
-        <v>96</v>
+      <c r="A331" s="1">
+        <v>329</v>
       </c>
       <c r="B331" s="2" t="s">
         <v>4</v>
@@ -6206,8 +6641,8 @@
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A332" s="6">
-        <v>97</v>
+      <c r="A332" s="1">
+        <v>330</v>
       </c>
       <c r="B332" s="2" t="s">
         <v>4</v>
@@ -6220,8 +6655,8 @@
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A333" s="6">
-        <v>98</v>
+      <c r="A333" s="1">
+        <v>331</v>
       </c>
       <c r="B333" s="2" t="s">
         <v>4</v>
@@ -6234,8 +6669,8 @@
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A334" s="6">
-        <v>99</v>
+      <c r="A334" s="1">
+        <v>332</v>
       </c>
       <c r="B334" s="2" t="s">
         <v>4</v>
@@ -6248,8 +6683,8 @@
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A335" s="6">
-        <v>100</v>
+      <c r="A335" s="1">
+        <v>333</v>
       </c>
       <c r="B335" s="2" t="s">
         <v>4</v>
@@ -6262,8 +6697,8 @@
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A336" s="6">
-        <v>101</v>
+      <c r="A336" s="1">
+        <v>334</v>
       </c>
       <c r="B336" s="2" t="s">
         <v>4</v>
@@ -6276,8 +6711,8 @@
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A337" s="6">
-        <v>102</v>
+      <c r="A337" s="1">
+        <v>335</v>
       </c>
       <c r="B337" s="2" t="s">
         <v>4</v>
@@ -6290,8 +6725,8 @@
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A338" s="6">
-        <v>103</v>
+      <c r="A338" s="1">
+        <v>336</v>
       </c>
       <c r="B338" s="2" t="s">
         <v>4</v>
@@ -6304,8 +6739,8 @@
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A339" s="6">
-        <v>104</v>
+      <c r="A339" s="1">
+        <v>337</v>
       </c>
       <c r="B339" s="2" t="s">
         <v>4</v>
@@ -6318,8 +6753,8 @@
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A340" s="6">
-        <v>105</v>
+      <c r="A340" s="1">
+        <v>338</v>
       </c>
       <c r="B340" s="2" t="s">
         <v>4</v>
@@ -6332,8 +6767,8 @@
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A341" s="6">
-        <v>106</v>
+      <c r="A341" s="1">
+        <v>339</v>
       </c>
       <c r="B341" s="2" t="s">
         <v>4</v>
@@ -6346,8 +6781,8 @@
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A342" s="6">
-        <v>107</v>
+      <c r="A342" s="1">
+        <v>340</v>
       </c>
       <c r="B342" s="2" t="s">
         <v>4</v>
@@ -6360,8 +6795,8 @@
       </c>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A343" s="6">
-        <v>108</v>
+      <c r="A343" s="1">
+        <v>341</v>
       </c>
       <c r="B343" s="2" t="s">
         <v>4</v>
@@ -6374,8 +6809,8 @@
       </c>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A344" s="6">
-        <v>109</v>
+      <c r="A344" s="1">
+        <v>342</v>
       </c>
       <c r="B344" s="2" t="s">
         <v>4</v>
@@ -6388,8 +6823,8 @@
       </c>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A345" s="6">
-        <v>110</v>
+      <c r="A345" s="1">
+        <v>343</v>
       </c>
       <c r="B345" s="2" t="s">
         <v>4</v>
@@ -6399,6 +6834,1532 @@
       </c>
       <c r="D345" s="6" t="s">
         <v>373</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A346" s="1">
+        <v>344</v>
+      </c>
+      <c r="B346" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C346" s="12">
+        <v>395</v>
+      </c>
+      <c r="D346" s="13" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A347" s="1">
+        <v>345</v>
+      </c>
+      <c r="B347" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C347" s="17">
+        <v>395</v>
+      </c>
+      <c r="D347" s="13" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A348" s="1">
+        <v>346</v>
+      </c>
+      <c r="B348" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C348" s="17">
+        <v>395</v>
+      </c>
+      <c r="D348" s="13" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A349" s="1">
+        <v>347</v>
+      </c>
+      <c r="B349" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C349" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D349" s="14" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A350" s="1">
+        <v>348</v>
+      </c>
+      <c r="B350" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C350" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D350" s="14" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A351" s="1">
+        <v>349</v>
+      </c>
+      <c r="B351" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C351" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D351" s="14" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A352" s="1">
+        <v>350</v>
+      </c>
+      <c r="B352" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C352" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D352" s="14" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A353" s="1">
+        <v>351</v>
+      </c>
+      <c r="B353" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C353" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D353" s="14" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A354" s="1">
+        <v>352</v>
+      </c>
+      <c r="B354" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C354" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D354" s="14" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A355" s="1">
+        <v>353</v>
+      </c>
+      <c r="B355" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C355" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D355" s="14" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A356" s="1">
+        <v>354</v>
+      </c>
+      <c r="B356" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C356" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D356" s="14" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A357" s="1">
+        <v>355</v>
+      </c>
+      <c r="B357" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C357" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D357" s="14" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A358" s="1">
+        <v>356</v>
+      </c>
+      <c r="B358" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C358" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D358" s="14" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A359" s="1">
+        <v>357</v>
+      </c>
+      <c r="B359" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C359" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D359" s="14" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A360" s="1">
+        <v>358</v>
+      </c>
+      <c r="B360" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C360" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D360" s="14" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A361" s="1">
+        <v>359</v>
+      </c>
+      <c r="B361" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C361" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D361" s="14" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A362" s="1">
+        <v>360</v>
+      </c>
+      <c r="B362" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C362" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D362" s="14" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A363" s="1">
+        <v>361</v>
+      </c>
+      <c r="B363" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C363" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D363" s="14" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A364" s="1">
+        <v>362</v>
+      </c>
+      <c r="B364" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C364" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="D364" s="14" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A365" s="1">
+        <v>363</v>
+      </c>
+      <c r="B365" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C365" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D365" s="14" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A366" s="1">
+        <v>364</v>
+      </c>
+      <c r="B366" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C366" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D366" s="14" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A367" s="1">
+        <v>365</v>
+      </c>
+      <c r="B367" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C367" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D367" s="14" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A368" s="1">
+        <v>366</v>
+      </c>
+      <c r="B368" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C368" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D368" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A369" s="1">
+        <v>367</v>
+      </c>
+      <c r="B369" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C369" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D369" s="14" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A370" s="1">
+        <v>368</v>
+      </c>
+      <c r="B370" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C370" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D370" s="14" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A371" s="1">
+        <v>369</v>
+      </c>
+      <c r="B371" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C371" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D371" s="14" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A372" s="1">
+        <v>370</v>
+      </c>
+      <c r="B372" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C372" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D372" s="14" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A373" s="1">
+        <v>371</v>
+      </c>
+      <c r="B373" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C373" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D373" s="14" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A374" s="1">
+        <v>372</v>
+      </c>
+      <c r="B374" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C374" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D374" s="14" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A375" s="1">
+        <v>373</v>
+      </c>
+      <c r="B375" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C375" s="12" t="s">
+        <v>480</v>
+      </c>
+      <c r="D375" s="14" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A376" s="1">
+        <v>374</v>
+      </c>
+      <c r="B376" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C376" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D376" s="15" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A377" s="1">
+        <v>375</v>
+      </c>
+      <c r="B377" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C377" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D377" s="15" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A378" s="1">
+        <v>376</v>
+      </c>
+      <c r="B378" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C378" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D378" s="15" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A379" s="1">
+        <v>377</v>
+      </c>
+      <c r="B379" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C379" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D379" s="15" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A380" s="1">
+        <v>378</v>
+      </c>
+      <c r="B380" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C380" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D380" s="15" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A381" s="1">
+        <v>379</v>
+      </c>
+      <c r="B381" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C381" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D381" s="15" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A382" s="1">
+        <v>380</v>
+      </c>
+      <c r="B382" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C382" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D382" s="15" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A383" s="1">
+        <v>381</v>
+      </c>
+      <c r="B383" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C383" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D383" s="15" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A384" s="1">
+        <v>382</v>
+      </c>
+      <c r="B384" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C384" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D384" s="15" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A385" s="1">
+        <v>383</v>
+      </c>
+      <c r="B385" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C385" s="15" t="s">
+        <v>481</v>
+      </c>
+      <c r="D385" s="15" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A386" s="1">
+        <v>384</v>
+      </c>
+      <c r="B386" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C386" s="15" t="s">
+        <v>482</v>
+      </c>
+      <c r="D386" s="15" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A387" s="1">
+        <v>385</v>
+      </c>
+      <c r="B387" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C387" s="15" t="s">
+        <v>483</v>
+      </c>
+      <c r="D387" s="15" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A388" s="1">
+        <v>386</v>
+      </c>
+      <c r="B388" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C388" s="15" t="s">
+        <v>484</v>
+      </c>
+      <c r="D388" s="15" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A389" s="1">
+        <v>387</v>
+      </c>
+      <c r="B389" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C389" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="D389" s="15" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A390" s="1">
+        <v>388</v>
+      </c>
+      <c r="B390" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C390" s="15" t="s">
+        <v>485</v>
+      </c>
+      <c r="D390" s="15" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A391" s="1">
+        <v>389</v>
+      </c>
+      <c r="B391" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C391" s="15" t="s">
+        <v>486</v>
+      </c>
+      <c r="D391" s="15" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A392" s="1">
+        <v>390</v>
+      </c>
+      <c r="B392" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="C392" s="15" t="s">
+        <v>487</v>
+      </c>
+      <c r="D392" s="15" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A393" s="1">
+        <v>391</v>
+      </c>
+      <c r="B393" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C393" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="D393" s="15" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A394" s="1">
+        <v>392</v>
+      </c>
+      <c r="B394" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C394" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="D394" s="15" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A395" s="1">
+        <v>393</v>
+      </c>
+      <c r="B395" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C395" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="D395" s="15" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A396" s="1">
+        <v>394</v>
+      </c>
+      <c r="B396" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C396" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="D396" s="15" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A397" s="1">
+        <v>395</v>
+      </c>
+      <c r="B397" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C397" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="D397" s="15" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A398" s="1">
+        <v>396</v>
+      </c>
+      <c r="B398" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C398" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="D398" s="15" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A399" s="1">
+        <v>397</v>
+      </c>
+      <c r="B399" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C399" s="15" t="s">
+        <v>488</v>
+      </c>
+      <c r="D399" s="15" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A400" s="1">
+        <v>398</v>
+      </c>
+      <c r="B400" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C400" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="D400" s="15" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A401" s="1">
+        <v>399</v>
+      </c>
+      <c r="B401" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C401" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="D401" s="15" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A402" s="1">
+        <v>400</v>
+      </c>
+      <c r="B402" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C402" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="D402" s="15" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A403" s="1">
+        <v>401</v>
+      </c>
+      <c r="B403" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C403" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="D403" s="15" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A404" s="1">
+        <v>402</v>
+      </c>
+      <c r="B404" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C404" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="D404" s="15" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A405" s="1">
+        <v>403</v>
+      </c>
+      <c r="B405" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C405" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="D405" s="15" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A406" s="1">
+        <v>404</v>
+      </c>
+      <c r="B406" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C406" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="D406" s="15" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A407" s="1">
+        <v>405</v>
+      </c>
+      <c r="B407" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C407" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="D407" s="15" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A408" s="1">
+        <v>406</v>
+      </c>
+      <c r="B408" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C408" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="D408" s="15" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A409" s="1">
+        <v>407</v>
+      </c>
+      <c r="B409" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C409" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="D409" s="15" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A410" s="1">
+        <v>408</v>
+      </c>
+      <c r="B410" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C410" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="D410" s="15" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A411" s="1">
+        <v>409</v>
+      </c>
+      <c r="B411" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C411" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="D411" s="15" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A412" s="1">
+        <v>410</v>
+      </c>
+      <c r="B412" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C412" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="D412" s="15" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A413" s="1">
+        <v>411</v>
+      </c>
+      <c r="B413" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C413" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="D413" s="15" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A414" s="1">
+        <v>412</v>
+      </c>
+      <c r="B414" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C414" s="15" t="s">
+        <v>494</v>
+      </c>
+      <c r="D414" s="15" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A415" s="1">
+        <v>413</v>
+      </c>
+      <c r="B415" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C415" s="15" t="s">
+        <v>495</v>
+      </c>
+      <c r="D415" s="15" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A416" s="1">
+        <v>414</v>
+      </c>
+      <c r="B416" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C416" s="15" t="s">
+        <v>493</v>
+      </c>
+      <c r="D416" s="15" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A417" s="1">
+        <v>415</v>
+      </c>
+      <c r="B417" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C417" s="15" t="s">
+        <v>496</v>
+      </c>
+      <c r="D417" s="15" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A418" s="1">
+        <v>416</v>
+      </c>
+      <c r="B418" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C418" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="D418" s="15" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A419" s="1">
+        <v>417</v>
+      </c>
+      <c r="B419" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C419" s="15" t="s">
+        <v>498</v>
+      </c>
+      <c r="D419" s="15" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A420" s="1">
+        <v>418</v>
+      </c>
+      <c r="B420" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C420" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="D420" s="15" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A421" s="1">
+        <v>419</v>
+      </c>
+      <c r="B421" s="15" t="s">
+        <v>506</v>
+      </c>
+      <c r="C421" s="15" t="s">
+        <v>489</v>
+      </c>
+      <c r="D421" s="15" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A422" s="1">
+        <v>420</v>
+      </c>
+      <c r="B422" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="C422" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D422" s="14" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A423" s="1">
+        <v>421</v>
+      </c>
+      <c r="B423" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="C423" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D423" s="14" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A424" s="1">
+        <v>422</v>
+      </c>
+      <c r="B424" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="C424" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D424" s="14" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A425" s="1">
+        <v>423</v>
+      </c>
+      <c r="B425" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="C425" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D425" s="14" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A426" s="1">
+        <v>424</v>
+      </c>
+      <c r="B426" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="C426" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D426" s="14" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A427" s="1">
+        <v>425</v>
+      </c>
+      <c r="B427" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="C427" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D427" s="14" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A428" s="1">
+        <v>426</v>
+      </c>
+      <c r="B428" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="C428" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D428" s="14" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A429" s="1">
+        <v>427</v>
+      </c>
+      <c r="B429" s="15" t="s">
+        <v>507</v>
+      </c>
+      <c r="C429" s="15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D429" s="14" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A430" s="1">
+        <v>428</v>
+      </c>
+      <c r="B430" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C430" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="D430" s="15" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A431" s="1">
+        <v>429</v>
+      </c>
+      <c r="B431" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C431" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="D431" s="15" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A432" s="1">
+        <v>430</v>
+      </c>
+      <c r="B432" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C432" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="D432" s="15" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A433" s="1">
+        <v>431</v>
+      </c>
+      <c r="B433" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C433" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="D433" s="15" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A434" s="1">
+        <v>432</v>
+      </c>
+      <c r="B434" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C434" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="D434" s="15" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A435" s="1">
+        <v>433</v>
+      </c>
+      <c r="B435" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C435" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="D435" s="15" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A436" s="1">
+        <v>434</v>
+      </c>
+      <c r="B436" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C436" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="D436" s="15" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A437" s="1">
+        <v>435</v>
+      </c>
+      <c r="B437" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C437" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="D437" s="15" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A438" s="1">
+        <v>436</v>
+      </c>
+      <c r="B438" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C438" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="D438" s="15" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A439" s="1">
+        <v>437</v>
+      </c>
+      <c r="B439" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C439" s="15" t="s">
+        <v>501</v>
+      </c>
+      <c r="D439" s="15" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="440" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A440" s="1">
+        <v>438</v>
+      </c>
+      <c r="B440" s="15" t="s">
+        <v>508</v>
+      </c>
+      <c r="C440" s="15" t="s">
+        <v>502</v>
+      </c>
+      <c r="D440" s="15" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="441" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A441" s="1">
+        <v>439</v>
+      </c>
+      <c r="B441" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="C441" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="D441" s="15" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="442" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A442" s="1">
+        <v>440</v>
+      </c>
+      <c r="B442" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="C442" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="D442" s="15" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="443" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A443" s="1">
+        <v>441</v>
+      </c>
+      <c r="B443" s="15" t="s">
+        <v>509</v>
+      </c>
+      <c r="C443" s="15" t="s">
+        <v>503</v>
+      </c>
+      <c r="D443" s="15" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="444" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A444" s="1">
+        <v>442</v>
+      </c>
+      <c r="B444" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C444" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="D444" s="16" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="445" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A445" s="1">
+        <v>443</v>
+      </c>
+      <c r="B445" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C445" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="D445" s="16" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="446" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A446" s="1">
+        <v>444</v>
+      </c>
+      <c r="B446" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C446" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="D446" s="16" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="447" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A447" s="1">
+        <v>445</v>
+      </c>
+      <c r="B447" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C447" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="D447" s="16" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="448" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A448" s="1">
+        <v>446</v>
+      </c>
+      <c r="B448" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C448" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="D448" s="16" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="449" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A449" s="1">
+        <v>447</v>
+      </c>
+      <c r="B449" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C449" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="D449" s="16" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="450" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A450" s="1">
+        <v>448</v>
+      </c>
+      <c r="B450" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C450" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="D450" s="16" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="451" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A451" s="1">
+        <v>449</v>
+      </c>
+      <c r="B451" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C451" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="D451" s="16" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="452" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A452" s="1">
+        <v>450</v>
+      </c>
+      <c r="B452" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C452" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="D452" s="16" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="453" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A453" s="1">
+        <v>451</v>
+      </c>
+      <c r="B453" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C453" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="D453" s="16" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="454" spans="1:4" ht="16" x14ac:dyDescent="0.2">
+      <c r="A454" s="1">
+        <v>452</v>
+      </c>
+      <c r="B454" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C454" s="16" t="s">
+        <v>504</v>
+      </c>
+      <c r="D454" s="16" t="s">
+        <v>477</v>
       </c>
     </row>
   </sheetData>
